--- a/data/trans_orig/MCS12_SP-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media del componente de salud mental (SF12)</t>
+          <t>Puntuación media del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,95; 53,02</t>
+          <t>50,9; 52,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,39; 51,27</t>
+          <t>49,4; 51,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,29; 50,76</t>
+          <t>48,42; 50,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,35; 54,46</t>
+          <t>53,22; 54,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,47; 51,73</t>
+          <t>49,31; 51,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,38; 46,32</t>
+          <t>43,4; 46,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,47; 48,12</t>
+          <t>45,33; 48,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,04; 54,0</t>
+          <t>53,0; 53,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,53; 52,08</t>
+          <t>50,61; 52,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,76; 48,55</t>
+          <t>46,74; 48,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,27; 49,17</t>
+          <t>47,39; 49,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,36; 54,11</t>
+          <t>53,32; 54,1</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,7; 52,03</t>
+          <t>50,73; 52,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,5; 55,2</t>
+          <t>53,54; 55,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,79; 56,03</t>
+          <t>54,89; 56,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,98; 54,76</t>
+          <t>52,88; 54,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,37; 49,07</t>
+          <t>47,36; 49,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,38; 52,38</t>
+          <t>50,41; 52,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,78; 54,36</t>
+          <t>52,69; 54,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,34; 52,79</t>
+          <t>51,37; 52,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49,26; 50,39</t>
+          <t>49,2; 50,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,28; 53,62</t>
+          <t>52,19; 53,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53,96; 55,01</t>
+          <t>54,02; 55,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,4; 53,59</t>
+          <t>52,43; 53,6</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,4; 55,39</t>
+          <t>54,35; 55,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,65; 53,43</t>
+          <t>51,72; 53,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,44; 53,48</t>
+          <t>52,37; 53,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,78; 55,41</t>
+          <t>53,69; 55,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,16; 54,41</t>
+          <t>53,18; 54,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,13; 51,15</t>
+          <t>49,21; 51,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,99; 52,37</t>
+          <t>51,02; 52,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,16; 53,67</t>
+          <t>52,21; 53,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,02; 54,75</t>
+          <t>53,95; 54,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,75; 52,03</t>
+          <t>50,8; 52,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,85; 52,76</t>
+          <t>51,91; 52,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,2; 54,27</t>
+          <t>53,15; 54,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,91; 54,11</t>
+          <t>52,92; 54,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,23; 51,85</t>
+          <t>50,31; 51,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,19; 52,9</t>
+          <t>51,15; 52,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,86; 55,03</t>
+          <t>52,86; 54,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,94; 52,64</t>
+          <t>51,01; 52,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,41; 47,65</t>
+          <t>45,37; 47,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,42; 50,05</t>
+          <t>47,54; 50,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,06; 53,57</t>
+          <t>51,13; 53,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,1; 53,17</t>
+          <t>52,21; 53,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,07; 49,4</t>
+          <t>48,07; 49,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49,62; 51,25</t>
+          <t>49,53; 51,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,19; 53,79</t>
+          <t>52,15; 53,82</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>49,76; 51,81</t>
+          <t>49,84; 51,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,65; 54,62</t>
+          <t>52,69; 54,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,89; 49,66</t>
+          <t>47,88; 49,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,06; 49,7</t>
+          <t>48,06; 49,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,02; 50,45</t>
+          <t>48,03; 50,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,15; 50,51</t>
+          <t>47,28; 50,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,49; 48,51</t>
+          <t>46,4; 48,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,28; 47,66</t>
+          <t>46,3; 47,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,29; 50,82</t>
+          <t>49,34; 50,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,29; 52,23</t>
+          <t>50,41; 52,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,49; 48,75</t>
+          <t>47,46; 48,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,35; 48,42</t>
+          <t>47,31; 48,44</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,18; 55,08</t>
+          <t>54,11; 55,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,92; 52,77</t>
+          <t>50,91; 52,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,45; 54,51</t>
+          <t>52,51; 54,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,73; 54,57</t>
+          <t>52,64; 54,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,07; 53,64</t>
+          <t>52,11; 53,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,22; 51,54</t>
+          <t>49,2; 51,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,59; 52,12</t>
+          <t>49,27; 51,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,81; 53,52</t>
+          <t>51,93; 53,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,32; 54,23</t>
+          <t>53,26; 54,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50,45; 51,93</t>
+          <t>50,47; 51,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,22; 53,02</t>
+          <t>51,32; 52,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52,6; 53,87</t>
+          <t>52,66; 53,86</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,26; 54,26</t>
+          <t>53,28; 54,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,47; 52,56</t>
+          <t>51,47; 52,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,15; 52,45</t>
+          <t>51,07; 52,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,87; 51,55</t>
+          <t>49,97; 51,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,04; 52,39</t>
+          <t>51,01; 52,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,13; 51,32</t>
+          <t>50,14; 51,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,18; 50,79</t>
+          <t>49,27; 50,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,7; 49,04</t>
+          <t>45,86; 48,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52,32; 53,12</t>
+          <t>52,3; 53,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50,94; 51,78</t>
+          <t>50,93; 51,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50,33; 51,38</t>
+          <t>50,33; 51,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,24; 49,94</t>
+          <t>47,04; 49,94</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>50,01; 51,23</t>
+          <t>50,0; 51,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,11; 51,37</t>
+          <t>50,13; 51,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,04; 52,93</t>
+          <t>52,05; 52,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51,51; 53,98</t>
+          <t>51,49; 53,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,76; 50,08</t>
+          <t>48,73; 50,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,86; 49,19</t>
+          <t>47,83; 49,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,01; 52,13</t>
+          <t>51,0; 52,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>48,5; 49,74</t>
+          <t>48,48; 49,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49,54; 50,48</t>
+          <t>49,5; 50,47</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49,12; 50,08</t>
+          <t>49,18; 50,12</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51,66; 52,41</t>
+          <t>51,64; 52,38</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,23; 52,72</t>
+          <t>50,24; 52,76</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52,31; 52,8</t>
+          <t>52,27; 52,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51,75; 52,32</t>
+          <t>51,78; 52,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52,17; 52,7</t>
+          <t>52,16; 52,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52,48; 53,31</t>
+          <t>52,48; 53,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50,47; 51,07</t>
+          <t>50,45; 51,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,86; 49,56</t>
+          <t>48,88; 49,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,31; 50,93</t>
+          <t>50,27; 50,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49,39; 50,96</t>
+          <t>49,35; 50,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,45; 51,86</t>
+          <t>51,47; 51,82</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50,4; 50,84</t>
+          <t>50,38; 50,83</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51,3; 51,71</t>
+          <t>51,32; 51,71</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50,98; 51,99</t>
+          <t>50,88; 52,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53,95</t>
+          <t>54,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>53,56</t>
+          <t>53,62</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,76</t>
+          <t>53,84</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,9; 52,92</t>
+          <t>51,04; 52,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,4; 51,29</t>
+          <t>49,27; 51,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,42; 50,81</t>
+          <t>48,42; 50,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,22; 54,42</t>
+          <t>53,53; 54,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,31; 51,85</t>
+          <t>49,33; 51,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,4; 46,25</t>
+          <t>43,34; 46,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,33; 48,16</t>
+          <t>45,34; 48,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,0; 53,99</t>
+          <t>53,14; 54,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,61; 52,1</t>
+          <t>50,59; 52,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,74; 48,57</t>
+          <t>46,7; 48,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,39; 49,16</t>
+          <t>47,37; 49,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,32; 54,1</t>
+          <t>53,49; 54,12</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,94</t>
+          <t>53,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,13</t>
+          <t>52,19</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,73; 52,07</t>
+          <t>50,7; 52,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,54; 55,29</t>
+          <t>53,62; 55,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,89; 56,05</t>
+          <t>54,89; 56,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,88; 54,8</t>
+          <t>52,93; 54,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,36; 49,08</t>
+          <t>47,39; 49,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,41; 52,44</t>
+          <t>50,25; 52,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,69; 54,27</t>
+          <t>52,79; 54,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,37; 52,86</t>
+          <t>51,4; 52,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49,2; 50,32</t>
+          <t>49,26; 50,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,19; 53,55</t>
+          <t>52,25; 53,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,02; 55,02</t>
+          <t>54,0; 55,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,43; 53,6</t>
+          <t>52,37; 53,57</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54,68</t>
+          <t>54,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,95</t>
+          <t>52,88</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,78</t>
+          <t>53,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,35; 55,36</t>
+          <t>54,37; 55,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,72; 53,46</t>
+          <t>51,74; 53,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,37; 53,47</t>
+          <t>52,43; 53,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,69; 55,36</t>
+          <t>53,51; 55,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,18; 54,45</t>
+          <t>53,22; 54,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,21; 51,14</t>
+          <t>49,15; 51,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,02; 52,4</t>
+          <t>51,01; 52,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,21; 53,67</t>
+          <t>52,05; 53,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,95; 54,77</t>
+          <t>54,0; 54,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,8; 52,06</t>
+          <t>50,7; 52,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,91; 52,76</t>
+          <t>51,85; 52,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,15; 54,29</t>
+          <t>53,0; 54,14</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54,12</t>
+          <t>54,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,24</t>
+          <t>51,59</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,99</t>
+          <t>52,8</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,92; 54,12</t>
+          <t>52,96; 54,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,31; 51,86</t>
+          <t>50,29; 51,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,15; 52,94</t>
+          <t>51,19; 52,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,86; 54,94</t>
+          <t>53,09; 54,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,01; 52,66</t>
+          <t>51,03; 52,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,37; 47,44</t>
+          <t>45,35; 47,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,54; 50,08</t>
+          <t>47,5; 50,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,13; 53,61</t>
+          <t>50,35; 52,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,21; 53,21</t>
+          <t>52,17; 53,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,07; 49,47</t>
+          <t>47,98; 49,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49,53; 51,16</t>
+          <t>49,63; 51,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,15; 53,82</t>
+          <t>51,96; 53,42</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48,94</t>
+          <t>49,16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47,0</t>
+          <t>47,18</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47,9</t>
+          <t>48,13</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>49,84; 51,96</t>
+          <t>49,77; 51,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,69; 54,57</t>
+          <t>52,72; 54,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,88; 49,65</t>
+          <t>47,94; 49,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,06; 49,69</t>
+          <t>48,38; 49,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,03; 50,3</t>
+          <t>48,02; 50,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,28; 50,54</t>
+          <t>47,35; 50,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,4; 48,36</t>
+          <t>46,57; 48,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,3; 47,7</t>
+          <t>46,42; 47,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,34; 50,82</t>
+          <t>49,2; 50,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,41; 52,31</t>
+          <t>50,36; 52,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,46; 48,73</t>
+          <t>47,47; 48,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,31; 48,44</t>
+          <t>47,61; 48,72</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53,79</t>
+          <t>53,83</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>52,76</t>
+          <t>52,77</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,28</t>
+          <t>53,3</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,11; 55,04</t>
+          <t>54,07; 55,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,91; 52,89</t>
+          <t>50,98; 52,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,51; 54,51</t>
+          <t>52,52; 54,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,64; 54,49</t>
+          <t>52,85; 54,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,11; 53,62</t>
+          <t>52,08; 53,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,2; 51,41</t>
+          <t>49,3; 51,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,27; 51,94</t>
+          <t>49,48; 52,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,93; 53,59</t>
+          <t>51,82; 53,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,26; 54,23</t>
+          <t>53,32; 54,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50,47; 51,89</t>
+          <t>50,31; 51,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,32; 52,98</t>
+          <t>51,33; 52,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52,66; 53,86</t>
+          <t>52,66; 53,84</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50,81</t>
+          <t>51,03</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>47,64</t>
+          <t>48,73</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,98</t>
+          <t>49,84</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,28; 54,24</t>
+          <t>53,25; 54,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,47; 52,54</t>
+          <t>51,47; 52,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,07; 52,39</t>
+          <t>51,2; 52,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,97; 51,71</t>
+          <t>50,11; 51,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,01; 52,29</t>
+          <t>51,01; 52,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,14; 51,33</t>
+          <t>50,08; 51,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,27; 50,8</t>
+          <t>49,21; 50,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,86; 48,98</t>
+          <t>48,0; 49,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52,3; 53,11</t>
+          <t>52,29; 53,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50,93; 51,79</t>
+          <t>50,94; 51,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50,33; 51,34</t>
+          <t>50,36; 51,38</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,04; 49,94</t>
+          <t>49,27; 50,36</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52,57</t>
+          <t>51,76</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49,14</t>
+          <t>49,27</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51,08</t>
+          <t>50,49</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>50,0; 51,27</t>
+          <t>50,0; 51,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,13; 51,44</t>
+          <t>50,13; 51,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,05; 52,96</t>
+          <t>52,03; 52,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51,49; 53,91</t>
+          <t>51,14; 52,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,73; 50,11</t>
+          <t>48,79; 50,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,83; 49,22</t>
+          <t>47,91; 49,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,0; 52,14</t>
+          <t>51,06; 52,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>48,48; 49,73</t>
+          <t>48,6; 49,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49,5; 50,47</t>
+          <t>49,56; 50,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49,18; 50,12</t>
+          <t>49,2; 50,14</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51,64; 52,38</t>
+          <t>51,7; 52,38</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,24; 52,76</t>
+          <t>50,06; 50,9</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52,82</t>
+          <t>52,64</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>50,46</t>
+          <t>50,68</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>51,61</t>
+          <t>51,63</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52,27; 52,77</t>
+          <t>52,29; 52,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51,78; 52,36</t>
+          <t>51,7; 52,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52,16; 52,7</t>
+          <t>52,19; 52,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52,48; 53,32</t>
+          <t>52,35; 52,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50,45; 51,07</t>
+          <t>50,46; 51,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,88; 49,57</t>
+          <t>48,86; 49,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,27; 50,92</t>
+          <t>50,27; 50,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49,35; 50,95</t>
+          <t>50,39; 50,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,47; 51,82</t>
+          <t>51,46; 51,85</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50,38; 50,83</t>
+          <t>50,39; 50,83</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51,32; 51,71</t>
+          <t>51,28; 51,71</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50,88; 52,0</t>
+          <t>51,43; 51,83</t>
         </is>
       </c>
     </row>
